--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01621592-40D5-4A55-8C5C-1E4008EE08C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9F4AA4-6248-4783-B69D-1E51BE5FA0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="114">
   <si>
     <t>No.</t>
   </si>
@@ -350,13 +350,43 @@
   </si>
   <si>
     <t>JEPS-2026-000336873</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000344023</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000344236</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000347792</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000348127</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000349364</t>
+  </si>
+  <si>
+    <t>MTC202609144682215</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000349820</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000350610</t>
+  </si>
+  <si>
+    <t>Wala pa confirmation</t>
+  </si>
+  <si>
+    <t>tip</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +419,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -638,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -729,6 +766,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1125,11 +1165,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="31">
+      <c r="J1" s="32">
         <v>6684</v>
       </c>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="34"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -1175,7 +1215,7 @@
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
         <v>3815</v>
       </c>
-      <c r="P2" s="34">
+      <c r="P2" s="35">
         <f>SUM(O2:O4)</f>
         <v>4865</v>
       </c>
@@ -1222,7 +1262,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>570</v>
       </c>
-      <c r="P3" s="34"/>
+      <c r="P3" s="35"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
@@ -1267,7 +1307,7 @@
         <f>SUMIFS(E:E, H:H, "")</f>
         <v>480</v>
       </c>
-      <c r="P4" s="34"/>
+      <c r="P4" s="35"/>
       <c r="R4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3345,7 +3385,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3366,7 +3406,7 @@
     <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -3391,16 +3431,16 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="31">
+      <c r="J1" s="32">
         <v>6684</v>
       </c>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="34"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -3438,14 +3478,17 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>540</v>
-      </c>
-      <c r="P2" s="34">
+        <v>1630</v>
+      </c>
+      <c r="P2" s="35">
         <f>SUM(O2:O4)</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1900</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f t="shared" ref="A3:A55" si="0">A2+1</f>
         <v>2</v>
@@ -3486,9 +3529,12 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="34"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P3" s="35"/>
+      <c r="R3" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3528,11 +3574,11 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>60</v>
-      </c>
-      <c r="P4" s="34"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="P4" s="35"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3569,7 +3615,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3605,7 +3651,7 @@
       </c>
       <c r="O6" s="25"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3646,7 +3692,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3687,7 +3733,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3723,7 +3769,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3752,7 +3798,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="15"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3781,7 +3827,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="15"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3808,7 +3854,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="15"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3835,58 +3881,82 @@
       <c r="K13" s="3"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="C14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="3">
+        <v>90</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="H14" s="15"/>
       <c r="J14" s="17"/>
       <c r="K14" s="3"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="3">
+        <v>90</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="H15" s="15"/>
       <c r="J15" s="17"/>
       <c r="K15" s="3"/>
       <c r="L15" s="15"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="C16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="3">
+        <v>90</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="H16" s="15"/>
       <c r="J16" s="17"/>
       <c r="K16" s="3"/>
@@ -3898,14 +3968,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="C17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="3">
+        <v>110</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="H17" s="15"/>
       <c r="J17" s="17"/>
       <c r="K17" s="3"/>
@@ -3917,14 +3995,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="3">
+        <v>90</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="H18" s="15"/>
       <c r="J18" s="17"/>
       <c r="K18" s="3"/>
@@ -3936,15 +4022,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="15"/>
+      <c r="C19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="3">
+        <v>90</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>32</v>
+      </c>
       <c r="J19" s="17"/>
       <c r="K19" s="3"/>
       <c r="L19" s="15"/>
@@ -3955,14 +4051,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="C20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="3">
+        <v>310</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="H20" s="15"/>
       <c r="J20" s="17"/>
       <c r="K20" s="3"/>
@@ -3974,34 +4078,52 @@
         <v>20</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="C21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="3">
+        <v>310</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>111</v>
+      </c>
       <c r="H21" s="15"/>
       <c r="J21" s="17"/>
       <c r="K21" s="3"/>
       <c r="L21" s="15"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="15"/>
+      <c r="C22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="3">
+        <v>310</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>32</v>
+      </c>
       <c r="J22" s="17"/>
       <c r="K22" s="3"/>
       <c r="L22" s="15"/>

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9F4AA4-6248-4783-B69D-1E51BE5FA0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842214D-EF1A-428A-A55F-5A32A5D19982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="115">
   <si>
     <t>No.</t>
   </si>
@@ -376,10 +376,13 @@
     <t>JEPS-2026-000350610</t>
   </si>
   <si>
-    <t>Wala pa confirmation</t>
-  </si>
-  <si>
     <t>tip</t>
+  </si>
+  <si>
+    <t>meonde</t>
+  </si>
+  <si>
+    <t>maputi</t>
   </si>
 </sst>
 </file>
@@ -3478,14 +3481,14 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>1630</v>
+        <v>2340</v>
       </c>
       <c r="P2" s="35">
         <f>SUM(O2:O4)</f>
-        <v>1900</v>
+        <v>2700</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3574,7 +3577,7 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="P4" s="35"/>
     </row>
@@ -4038,9 +4041,7 @@
       <c r="G19" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="H19" s="15" t="s">
-        <v>32</v>
-      </c>
+      <c r="H19" s="15"/>
       <c r="J19" s="17"/>
       <c r="K19" s="3"/>
       <c r="L19" s="15"/>
@@ -4099,7 +4100,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="15"/>
     </row>
-    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -4118,12 +4119,10 @@
       <c r="F22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>32</v>
-      </c>
+      <c r="G22" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="15"/>
       <c r="J22" s="17"/>
       <c r="K22" s="3"/>
       <c r="L22" s="15"/>
@@ -4134,14 +4133,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="C23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="3">
+        <v>310</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>114</v>
+      </c>
       <c r="H23" s="15"/>
       <c r="J23" s="17"/>
       <c r="K23" s="3"/>

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842214D-EF1A-428A-A55F-5A32A5D19982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703C39E8-5DB7-4246-8072-75421FCF9D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="125">
   <si>
     <t>No.</t>
   </si>
@@ -376,13 +376,47 @@
     <t>JEPS-2026-000350610</t>
   </si>
   <si>
-    <t>tip</t>
-  </si>
-  <si>
     <t>meonde</t>
   </si>
   <si>
     <t>maputi</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000380718</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000381351</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000387294</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000401034</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000401187</t>
+  </si>
+  <si>
+    <t>DEPOSIT OF FORFEITED
+MONEY EXHIBITS DUE TO THE
+GENERAL FUND</t>
+  </si>
+  <si>
+    <t>na confiscate na money</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000401411</t>
+  </si>
+  <si>
+    <t>FINES ON CRIMINAL CASES
+(EXCEPT DRUG CASES) - OCA
+CIR. NO. 26-2018</t>
+  </si>
+  <si>
+    <t>Fine after ng hearing</t>
   </si>
 </sst>
 </file>
@@ -460,7 +494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -674,11 +708,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -770,8 +817,37 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1168,11 +1244,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="32">
+      <c r="J1" s="43">
         <v>6684</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -1218,7 +1294,7 @@
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
         <v>3815</v>
       </c>
-      <c r="P2" s="35">
+      <c r="P2" s="46">
         <f>SUM(O2:O4)</f>
         <v>4865</v>
       </c>
@@ -1265,7 +1341,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>570</v>
       </c>
-      <c r="P3" s="35"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
@@ -1310,7 +1386,7 @@
         <f>SUMIFS(E:E, H:H, "")</f>
         <v>480</v>
       </c>
-      <c r="P4" s="35"/>
+      <c r="P4" s="46"/>
       <c r="R4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3342,40 +3418,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D4D6AF-B61D-464D-9E7F-C6E9749645A3}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3388,12 +3481,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3409,14 +3502,14 @@
     <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="22" t="s">
@@ -3434,21 +3527,21 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="32">
+      <c r="J1" s="43">
         <v>6684</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="3">
@@ -3481,23 +3574,20 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>2340</v>
-      </c>
-      <c r="P2" s="35">
+        <v>310</v>
+      </c>
+      <c r="P2" s="46">
         <f>SUM(O2:O4)</f>
-        <v>2700</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f t="shared" ref="A3:A55" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="3">
@@ -3532,18 +3622,15 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="35"/>
-      <c r="R3" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P3" s="46"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D4" s="3">
@@ -3577,17 +3664,17 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>360</v>
-      </c>
-      <c r="P4" s="35"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="P4" s="46"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D5" s="3">
@@ -3618,13 +3705,13 @@
       <c r="N5" s="2"/>
       <c r="O5" s="9"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D6" s="3">
@@ -3654,13 +3741,13 @@
       </c>
       <c r="O6" s="25"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="3">
@@ -3695,13 +3782,13 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="3">
@@ -3733,16 +3820,16 @@
         <v>92</v>
       </c>
       <c r="O8" s="1">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="34" t="s">
         <v>86</v>
       </c>
       <c r="D9" s="3">
@@ -3769,16 +3856,16 @@
       </c>
       <c r="O9" s="1">
         <f>O8-O7</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="34" t="s">
         <v>86</v>
       </c>
       <c r="D10" s="3">
@@ -3801,13 +3888,13 @@
       <c r="K10" s="3"/>
       <c r="L10" s="15"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="3">
@@ -3830,13 +3917,13 @@
       <c r="K11" s="3"/>
       <c r="L11" s="15"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="34" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="3">
@@ -3852,18 +3939,20 @@
       <c r="G12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="15">
+        <v>3</v>
+      </c>
       <c r="J12" s="17"/>
       <c r="K12" s="3"/>
       <c r="L12" s="15"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="34" t="s">
         <v>87</v>
       </c>
       <c r="D13" s="3">
@@ -3879,18 +3968,20 @@
       <c r="G13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="15"/>
+      <c r="H13" s="15">
+        <v>3</v>
+      </c>
       <c r="J13" s="17"/>
       <c r="K13" s="3"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="3">
@@ -3906,18 +3997,20 @@
       <c r="G14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="15"/>
+      <c r="H14" s="15">
+        <v>3</v>
+      </c>
       <c r="J14" s="17"/>
       <c r="K14" s="3"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="3">
@@ -3933,18 +4026,20 @@
       <c r="G15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="15"/>
+      <c r="H15" s="15">
+        <v>3</v>
+      </c>
       <c r="J15" s="17"/>
       <c r="K15" s="3"/>
       <c r="L15" s="15"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="3">
@@ -3960,18 +4055,20 @@
       <c r="G16" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="15"/>
+      <c r="H16" s="15">
+        <v>3</v>
+      </c>
       <c r="J16" s="17"/>
       <c r="K16" s="3"/>
       <c r="L16" s="15"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
@@ -3987,18 +4084,20 @@
       <c r="G17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H17" s="15"/>
+      <c r="H17" s="15">
+        <v>3</v>
+      </c>
       <c r="J17" s="17"/>
       <c r="K17" s="3"/>
       <c r="L17" s="15"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="34" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
@@ -4014,45 +4113,49 @@
       <c r="G18" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H18" s="15"/>
+      <c r="H18" s="15">
+        <v>3</v>
+      </c>
       <c r="J18" s="17"/>
       <c r="K18" s="3"/>
       <c r="L18" s="15"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="39">
         <v>90</v>
       </c>
-      <c r="E19" s="3">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="E19" s="39">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F19" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="H19" s="15"/>
+      <c r="H19" s="41" t="s">
+        <v>32</v>
+      </c>
       <c r="J19" s="17"/>
       <c r="K19" s="3"/>
       <c r="L19" s="15"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D20" s="3">
@@ -4068,18 +4171,23 @@
       <c r="G20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="15">
+        <v>3</v>
+      </c>
       <c r="J20" s="17"/>
       <c r="K20" s="3"/>
       <c r="L20" s="15"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="Q20" s="1">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D21" s="3">
@@ -4095,18 +4203,23 @@
       <c r="G21" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H21" s="15"/>
+      <c r="H21" s="15">
+        <v>3</v>
+      </c>
       <c r="J21" s="17"/>
       <c r="K21" s="3"/>
       <c r="L21" s="15"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="Q21" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="34" t="s">
         <v>85</v>
       </c>
       <c r="D22" s="3">
@@ -4119,162 +4232,230 @@
       <c r="F22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>113</v>
+      <c r="G22" s="31" t="s">
+        <v>112</v>
       </c>
       <c r="H22" s="15"/>
       <c r="J22" s="17"/>
       <c r="K22" s="3"/>
       <c r="L22" s="15"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="Q22" s="1">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="39">
         <v>310</v>
       </c>
-      <c r="E23" s="3">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="39">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F23" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="H23" s="15"/>
+      <c r="G23" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="41" t="s">
+        <v>32</v>
+      </c>
       <c r="J23" s="17"/>
       <c r="K23" s="3"/>
       <c r="L23" s="15"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="Q23" s="1">
+        <f>SUM(Q19:Q22)</f>
+        <v>6680</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="15"/>
+      <c r="C24" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="3">
+        <v>310</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H24" s="15">
+        <v>4</v>
+      </c>
       <c r="J24" s="17"/>
       <c r="K24" s="3"/>
       <c r="L24" s="15"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="15"/>
+      <c r="C25" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="3">
+        <v>100</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="15">
+        <v>4</v>
+      </c>
       <c r="J25" s="17"/>
       <c r="K25" s="3"/>
       <c r="L25" s="15"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="15"/>
+      <c r="C26" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="3">
+        <v>90</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="H26" s="15">
+        <v>4</v>
+      </c>
       <c r="J26" s="17"/>
       <c r="K26" s="3"/>
       <c r="L26" s="15"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="15"/>
+      <c r="C27" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="15">
+        <v>4</v>
+      </c>
       <c r="J27" s="17"/>
       <c r="K27" s="3"/>
       <c r="L27" s="15"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="15"/>
+      <c r="C28" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="15">
+        <v>5</v>
+      </c>
       <c r="J28" s="17"/>
       <c r="K28" s="3"/>
       <c r="L28" s="15"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="15"/>
+      <c r="C29" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>30</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="15">
+        <v>5</v>
+      </c>
       <c r="J29" s="17"/>
       <c r="K29" s="3"/>
       <c r="L29" s="15"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="3"/>
-      <c r="C30" s="5"/>
+      <c r="C30" s="34"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4287,13 +4468,13 @@
       <c r="K30" s="3"/>
       <c r="L30" s="15"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="5"/>
+      <c r="C31" s="34"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4306,13 +4487,13 @@
       <c r="K31" s="3"/>
       <c r="L31" s="15"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="5"/>
+      <c r="C32" s="34"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4331,7 +4512,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="5"/>
+      <c r="C33" s="34"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4350,7 +4531,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="5"/>
+      <c r="C34" s="34"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4369,7 +4550,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="5"/>
+      <c r="C35" s="34"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4385,7 +4566,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="5"/>
+      <c r="C36" s="34"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4401,7 +4582,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="5"/>
+      <c r="C37" s="34"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4417,7 +4598,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3"/>
-      <c r="C38" s="5"/>
+      <c r="C38" s="34"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4433,7 +4614,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="5"/>
+      <c r="C39" s="34"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4449,7 +4630,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="3"/>
-      <c r="C40" s="5"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4465,7 +4646,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="5"/>
+      <c r="C41" s="34"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4481,7 +4662,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="3"/>
-      <c r="C42" s="5"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4497,7 +4678,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
+      <c r="C43" s="35"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4513,7 +4694,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
+      <c r="C44" s="35"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4529,7 +4710,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3"/>
-      <c r="C45" s="5"/>
+      <c r="C45" s="34"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4545,7 +4726,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="3"/>
-      <c r="C46" s="5"/>
+      <c r="C46" s="34"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4561,7 +4742,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
+      <c r="C47" s="35"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4577,7 +4758,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
+      <c r="C48" s="35"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4593,7 +4774,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3"/>
-      <c r="C49" s="5"/>
+      <c r="C49" s="34"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4611,7 +4792,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="3"/>
-      <c r="C50" s="5"/>
+      <c r="C50" s="34"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4629,7 +4810,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3"/>
-      <c r="C51" s="5"/>
+      <c r="C51" s="34"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4647,7 +4828,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="3"/>
-      <c r="C52" s="5"/>
+      <c r="C52" s="34"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4665,7 +4846,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4683,7 +4864,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="3"/>
-      <c r="C54" s="5"/>
+      <c r="C54" s="34"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4699,7 +4880,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3"/>
-      <c r="C55" s="5"/>
+      <c r="C55" s="34"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4715,7 +4896,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
+      <c r="C56" s="35"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4731,7 +4912,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
+      <c r="C57" s="35"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4747,7 +4928,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="C58" s="35"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4763,7 +4944,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
+      <c r="C59" s="35"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4779,7 +4960,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
+      <c r="C60" s="35"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4795,7 +4976,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
+      <c r="C61" s="35"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4811,7 +4992,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
+      <c r="C62" s="35"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4827,7 +5008,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
+      <c r="C63" s="35"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4843,7 +5024,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
+      <c r="C64" s="35"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4859,7 +5040,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
+      <c r="C65" s="35"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4875,7 +5056,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
+      <c r="C66" s="35"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4891,7 +5072,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="C67" s="35"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4907,7 +5088,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
+      <c r="C68" s="35"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3" t="str">
         <f t="shared" ref="E68:E131" si="3">IF(D68&gt;0,30,"")</f>
@@ -4923,7 +5104,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
+      <c r="C69" s="35"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3" t="str">
         <f t="shared" si="3"/>
@@ -4939,7 +5120,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
+      <c r="C70" s="35"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3" t="str">
         <f t="shared" si="3"/>
@@ -4955,7 +5136,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
+      <c r="C71" s="35"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3" t="str">
         <f t="shared" si="3"/>
@@ -4971,7 +5152,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
+      <c r="C72" s="35"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3" t="str">
         <f t="shared" si="3"/>
@@ -4987,7 +5168,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
+      <c r="C73" s="35"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5003,7 +5184,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
+      <c r="C74" s="35"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5019,7 +5200,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="C75" s="35"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5035,7 +5216,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
+      <c r="C76" s="35"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5051,7 +5232,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
+      <c r="C77" s="35"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5067,7 +5248,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
+      <c r="C78" s="35"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5083,7 +5264,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
+      <c r="C79" s="35"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5099,7 +5280,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
+      <c r="C80" s="35"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5115,7 +5296,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
+      <c r="C81" s="35"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5131,7 +5312,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
+      <c r="C82" s="35"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5147,7 +5328,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="C83" s="35"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5163,7 +5344,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
+      <c r="C84" s="35"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5179,7 +5360,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
+      <c r="C85" s="35"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5195,7 +5376,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
+      <c r="C86" s="35"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5211,7 +5392,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
+      <c r="C87" s="35"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5227,7 +5408,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
+      <c r="C88" s="35"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5243,7 +5424,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
+      <c r="C89" s="35"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5259,7 +5440,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
+      <c r="C90" s="35"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5275,7 +5456,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
+      <c r="C91" s="35"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5291,7 +5472,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
+      <c r="C92" s="35"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5307,7 +5488,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
+      <c r="C93" s="35"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5323,7 +5504,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
+      <c r="C94" s="35"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5339,7 +5520,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
+      <c r="C95" s="35"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5355,7 +5536,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
+      <c r="C96" s="35"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5371,7 +5552,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
+      <c r="C97" s="35"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5387,7 +5568,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
+      <c r="C98" s="35"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5403,7 +5584,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="C99" s="35"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5419,7 +5600,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
+      <c r="C100" s="35"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5435,7 +5616,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
+      <c r="C101" s="35"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5451,7 +5632,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
+      <c r="C102" s="36"/>
       <c r="D102" s="2"/>
       <c r="E102" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5467,7 +5648,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
+      <c r="C103" s="36"/>
       <c r="D103" s="2"/>
       <c r="E103" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5483,7 +5664,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="C104" s="36"/>
       <c r="D104" s="2"/>
       <c r="E104" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5499,7 +5680,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
+      <c r="C105" s="36"/>
       <c r="D105" s="2"/>
       <c r="E105" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5515,7 +5696,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
+      <c r="C106" s="36"/>
       <c r="D106" s="2"/>
       <c r="E106" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5531,7 +5712,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
+      <c r="C107" s="36"/>
       <c r="D107" s="2"/>
       <c r="E107" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5547,7 +5728,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
+      <c r="C108" s="36"/>
       <c r="D108" s="2"/>
       <c r="E108" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5563,7 +5744,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
+      <c r="C109" s="36"/>
       <c r="D109" s="2"/>
       <c r="E109" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5579,7 +5760,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
+      <c r="C110" s="36"/>
       <c r="D110" s="2"/>
       <c r="E110" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5595,7 +5776,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
+      <c r="C111" s="36"/>
       <c r="D111" s="2"/>
       <c r="E111" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5611,7 +5792,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
+      <c r="C112" s="36"/>
       <c r="D112" s="2"/>
       <c r="E112" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5627,7 +5808,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
+      <c r="C113" s="36"/>
       <c r="D113" s="2"/>
       <c r="E113" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5643,7 +5824,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
+      <c r="C114" s="36"/>
       <c r="D114" s="2"/>
       <c r="E114" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5659,7 +5840,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
+      <c r="C115" s="36"/>
       <c r="D115" s="2"/>
       <c r="E115" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5675,7 +5856,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
+      <c r="C116" s="36"/>
       <c r="D116" s="2"/>
       <c r="E116" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5691,7 +5872,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
+      <c r="C117" s="36"/>
       <c r="D117" s="2"/>
       <c r="E117" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5707,7 +5888,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
+      <c r="C118" s="36"/>
       <c r="D118" s="2"/>
       <c r="E118" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5723,7 +5904,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
+      <c r="C119" s="36"/>
       <c r="D119" s="2"/>
       <c r="E119" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5739,7 +5920,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
+      <c r="C120" s="36"/>
       <c r="D120" s="2"/>
       <c r="E120" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5755,7 +5936,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
+      <c r="C121" s="36"/>
       <c r="D121" s="2"/>
       <c r="E121" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5771,7 +5952,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
+      <c r="C122" s="36"/>
       <c r="D122" s="2"/>
       <c r="E122" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5787,7 +5968,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
+      <c r="C123" s="36"/>
       <c r="D123" s="2"/>
       <c r="E123" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5803,7 +5984,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
+      <c r="C124" s="36"/>
       <c r="D124" s="2"/>
       <c r="E124" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5819,7 +6000,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
+      <c r="C125" s="36"/>
       <c r="D125" s="2"/>
       <c r="E125" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5835,7 +6016,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
+      <c r="C126" s="36"/>
       <c r="D126" s="2"/>
       <c r="E126" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5851,7 +6032,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
+      <c r="C127" s="36"/>
       <c r="D127" s="2"/>
       <c r="E127" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5867,7 +6048,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
+      <c r="C128" s="36"/>
       <c r="D128" s="2"/>
       <c r="E128" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5883,7 +6064,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
+      <c r="C129" s="36"/>
       <c r="D129" s="2"/>
       <c r="E129" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5899,7 +6080,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
+      <c r="C130" s="36"/>
       <c r="D130" s="2"/>
       <c r="E130" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5915,7 +6096,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
+      <c r="C131" s="36"/>
       <c r="D131" s="2"/>
       <c r="E131" s="3" t="str">
         <f t="shared" si="3"/>
@@ -5931,7 +6112,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
+      <c r="C132" s="36"/>
       <c r="D132" s="2"/>
       <c r="E132" s="3" t="str">
         <f t="shared" ref="E132:E195" si="5">IF(D132&gt;0,30,"")</f>
@@ -5947,7 +6128,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
+      <c r="C133" s="36"/>
       <c r="D133" s="2"/>
       <c r="E133" s="3" t="str">
         <f t="shared" si="5"/>
@@ -5963,7 +6144,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
+      <c r="C134" s="36"/>
       <c r="D134" s="2"/>
       <c r="E134" s="3" t="str">
         <f t="shared" si="5"/>
@@ -5979,7 +6160,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
+      <c r="C135" s="36"/>
       <c r="D135" s="2"/>
       <c r="E135" s="3" t="str">
         <f t="shared" si="5"/>
@@ -5995,7 +6176,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
+      <c r="C136" s="36"/>
       <c r="D136" s="2"/>
       <c r="E136" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6011,7 +6192,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
+      <c r="C137" s="36"/>
       <c r="D137" s="2"/>
       <c r="E137" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6027,7 +6208,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
+      <c r="C138" s="36"/>
       <c r="D138" s="2"/>
       <c r="E138" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6043,7 +6224,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
+      <c r="C139" s="36"/>
       <c r="D139" s="2"/>
       <c r="E139" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6059,7 +6240,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
+      <c r="C140" s="36"/>
       <c r="D140" s="2"/>
       <c r="E140" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6075,7 +6256,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
+      <c r="C141" s="36"/>
       <c r="D141" s="2"/>
       <c r="E141" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6091,7 +6272,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
+      <c r="C142" s="36"/>
       <c r="D142" s="2"/>
       <c r="E142" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6107,7 +6288,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
+      <c r="C143" s="36"/>
       <c r="D143" s="2"/>
       <c r="E143" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6123,7 +6304,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
+      <c r="C144" s="36"/>
       <c r="D144" s="2"/>
       <c r="E144" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6139,7 +6320,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
+      <c r="C145" s="36"/>
       <c r="D145" s="2"/>
       <c r="E145" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6155,7 +6336,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
+      <c r="C146" s="36"/>
       <c r="D146" s="2"/>
       <c r="E146" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6171,7 +6352,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
+      <c r="C147" s="36"/>
       <c r="D147" s="2"/>
       <c r="E147" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6187,7 +6368,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
+      <c r="C148" s="36"/>
       <c r="D148" s="2"/>
       <c r="E148" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6203,7 +6384,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
+      <c r="C149" s="36"/>
       <c r="D149" s="2"/>
       <c r="E149" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6219,7 +6400,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
+      <c r="C150" s="36"/>
       <c r="D150" s="2"/>
       <c r="E150" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6235,7 +6416,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
+      <c r="C151" s="36"/>
       <c r="D151" s="2"/>
       <c r="E151" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6251,7 +6432,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
+      <c r="C152" s="36"/>
       <c r="D152" s="2"/>
       <c r="E152" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6267,7 +6448,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
+      <c r="C153" s="36"/>
       <c r="D153" s="2"/>
       <c r="E153" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6283,7 +6464,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
+      <c r="C154" s="36"/>
       <c r="D154" s="2"/>
       <c r="E154" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6299,7 +6480,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
+      <c r="C155" s="36"/>
       <c r="D155" s="2"/>
       <c r="E155" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6315,7 +6496,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
+      <c r="C156" s="36"/>
       <c r="D156" s="2"/>
       <c r="E156" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6331,7 +6512,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
+      <c r="C157" s="36"/>
       <c r="D157" s="2"/>
       <c r="E157" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6347,7 +6528,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
+      <c r="C158" s="36"/>
       <c r="D158" s="2"/>
       <c r="E158" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6363,7 +6544,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
+      <c r="C159" s="36"/>
       <c r="D159" s="2"/>
       <c r="E159" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6379,7 +6560,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
+      <c r="C160" s="36"/>
       <c r="D160" s="2"/>
       <c r="E160" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6395,7 +6576,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
+      <c r="C161" s="36"/>
       <c r="D161" s="2"/>
       <c r="E161" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6411,7 +6592,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
+      <c r="C162" s="36"/>
       <c r="D162" s="2"/>
       <c r="E162" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6427,7 +6608,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
+      <c r="C163" s="36"/>
       <c r="D163" s="2"/>
       <c r="E163" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6443,7 +6624,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
+      <c r="C164" s="36"/>
       <c r="D164" s="2"/>
       <c r="E164" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6459,7 +6640,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
+      <c r="C165" s="36"/>
       <c r="D165" s="2"/>
       <c r="E165" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6475,7 +6656,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
+      <c r="C166" s="36"/>
       <c r="D166" s="2"/>
       <c r="E166" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6491,7 +6672,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
+      <c r="C167" s="36"/>
       <c r="D167" s="2"/>
       <c r="E167" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6507,7 +6688,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
+      <c r="C168" s="36"/>
       <c r="D168" s="2"/>
       <c r="E168" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6523,7 +6704,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
+      <c r="C169" s="36"/>
       <c r="D169" s="2"/>
       <c r="E169" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6539,7 +6720,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
+      <c r="C170" s="36"/>
       <c r="D170" s="2"/>
       <c r="E170" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6555,7 +6736,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
+      <c r="C171" s="36"/>
       <c r="D171" s="2"/>
       <c r="E171" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6571,7 +6752,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
+      <c r="C172" s="36"/>
       <c r="D172" s="2"/>
       <c r="E172" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6587,7 +6768,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
+      <c r="C173" s="36"/>
       <c r="D173" s="2"/>
       <c r="E173" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6603,7 +6784,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2"/>
-      <c r="C174" s="2"/>
+      <c r="C174" s="36"/>
       <c r="D174" s="2"/>
       <c r="E174" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6619,7 +6800,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
+      <c r="C175" s="36"/>
       <c r="D175" s="2"/>
       <c r="E175" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6635,7 +6816,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
+      <c r="C176" s="36"/>
       <c r="D176" s="2"/>
       <c r="E176" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6651,7 +6832,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="2"/>
-      <c r="C177" s="2"/>
+      <c r="C177" s="36"/>
       <c r="D177" s="2"/>
       <c r="E177" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6667,7 +6848,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2"/>
-      <c r="C178" s="2"/>
+      <c r="C178" s="36"/>
       <c r="D178" s="2"/>
       <c r="E178" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6683,7 +6864,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="2"/>
-      <c r="C179" s="2"/>
+      <c r="C179" s="36"/>
       <c r="D179" s="2"/>
       <c r="E179" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6699,7 +6880,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2"/>
-      <c r="C180" s="2"/>
+      <c r="C180" s="36"/>
       <c r="D180" s="2"/>
       <c r="E180" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6715,7 +6896,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
+      <c r="C181" s="36"/>
       <c r="D181" s="2"/>
       <c r="E181" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6731,7 +6912,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
+      <c r="C182" s="36"/>
       <c r="D182" s="2"/>
       <c r="E182" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6747,7 +6928,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
+      <c r="C183" s="36"/>
       <c r="D183" s="2"/>
       <c r="E183" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6763,7 +6944,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
+      <c r="C184" s="36"/>
       <c r="D184" s="2"/>
       <c r="E184" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6779,7 +6960,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
+      <c r="C185" s="36"/>
       <c r="D185" s="2"/>
       <c r="E185" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6795,7 +6976,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
+      <c r="C186" s="36"/>
       <c r="D186" s="2"/>
       <c r="E186" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6811,7 +6992,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
+      <c r="C187" s="36"/>
       <c r="D187" s="2"/>
       <c r="E187" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6827,7 +7008,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
+      <c r="C188" s="36"/>
       <c r="D188" s="2"/>
       <c r="E188" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6843,7 +7024,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2"/>
-      <c r="C189" s="2"/>
+      <c r="C189" s="36"/>
       <c r="D189" s="2"/>
       <c r="E189" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6859,7 +7040,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
+      <c r="C190" s="36"/>
       <c r="D190" s="2"/>
       <c r="E190" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6875,7 +7056,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="2"/>
-      <c r="C191" s="2"/>
+      <c r="C191" s="36"/>
       <c r="D191" s="2"/>
       <c r="E191" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6891,7 +7072,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
+      <c r="C192" s="36"/>
       <c r="D192" s="2"/>
       <c r="E192" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6907,7 +7088,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
+      <c r="C193" s="36"/>
       <c r="D193" s="2"/>
       <c r="E193" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6923,7 +7104,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
+      <c r="C194" s="36"/>
       <c r="D194" s="2"/>
       <c r="E194" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6939,7 +7120,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
+      <c r="C195" s="36"/>
       <c r="D195" s="2"/>
       <c r="E195" s="3" t="str">
         <f t="shared" si="5"/>
@@ -6955,7 +7136,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
+      <c r="C196" s="36"/>
       <c r="D196" s="2"/>
       <c r="E196" s="3" t="str">
         <f t="shared" ref="E196:E201" si="7">IF(D196&gt;0,30,"")</f>
@@ -6971,7 +7152,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
+      <c r="C197" s="36"/>
       <c r="D197" s="2"/>
       <c r="E197" s="3" t="str">
         <f t="shared" si="7"/>
@@ -6987,7 +7168,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
+      <c r="C198" s="36"/>
       <c r="D198" s="2"/>
       <c r="E198" s="3" t="str">
         <f t="shared" si="7"/>
@@ -7003,7 +7184,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
+      <c r="C199" s="36"/>
       <c r="D199" s="2"/>
       <c r="E199" s="3" t="str">
         <f t="shared" si="7"/>
@@ -7019,7 +7200,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
+      <c r="C200" s="36"/>
       <c r="D200" s="2"/>
       <c r="E200" s="3" t="str">
         <f t="shared" si="7"/>
@@ -7035,7 +7216,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="29"/>
-      <c r="C201" s="29"/>
+      <c r="C201" s="37"/>
       <c r="D201" s="29"/>
       <c r="E201" s="3" t="str">
         <f t="shared" si="7"/>

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703C39E8-5DB7-4246-8072-75421FCF9D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0471BF6-E09F-4A06-AADD-F3BC8B2EEF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="136">
   <si>
     <t>No.</t>
   </si>
@@ -374,9 +374,6 @@
   </si>
   <si>
     <t>JEPS-2026-000350610</t>
-  </si>
-  <si>
-    <t>meonde</t>
   </si>
   <si>
     <t>maputi</t>
@@ -417,6 +414,42 @@
   </si>
   <si>
     <t>Fine after ng hearing</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000409418</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000410523</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000410290</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000413773</t>
+  </si>
+  <si>
+    <t>Nelbelyn Omosura</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000447618</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000450896</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000458709</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000475785</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000478895</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000480534</t>
+  </si>
+  <si>
+    <t>Utanhg</t>
   </si>
 </sst>
 </file>
@@ -3457,18 +3490,18 @@
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s">
         <v>120</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" t="s">
         <v>123</v>
-      </c>
-      <c r="B8" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3481,7 +3514,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:U201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3502,7 +3535,7 @@
     <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -3536,7 +3569,7 @@
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -3574,14 +3607,14 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>310</v>
+        <v>1080</v>
       </c>
       <c r="P2" s="46">
         <f>SUM(O2:O4)</f>
-        <v>340</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f t="shared" ref="A3:A55" si="0">A2+1</f>
         <v>2</v>
@@ -3624,7 +3657,7 @@
       </c>
       <c r="P3" s="46"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3664,11 +3697,14 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="P4" s="46"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T4" s="1">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3704,8 +3740,15 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="9"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="T5" s="1">
+        <f>P2-T4</f>
+        <v>355</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3741,7 +3784,7 @@
       </c>
       <c r="O6" s="25"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3782,7 +3825,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3820,10 +3863,10 @@
         <v>92</v>
       </c>
       <c r="O8" s="1">
-        <v>2310</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3856,10 +3899,10 @@
       </c>
       <c r="O9" s="1">
         <f>O8-O7</f>
-        <v>750</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3888,7 +3931,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="15"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3917,7 +3960,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="15"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3946,7 +3989,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="15"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3975,7 +4018,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -4004,7 +4047,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -4033,7 +4076,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="15"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -4062,7 +4105,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="15"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -4091,7 +4134,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="15"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -4120,7 +4163,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="15"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -4149,7 +4192,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="15"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -4177,11 +4220,8 @@
       <c r="J20" s="17"/>
       <c r="K20" s="3"/>
       <c r="L20" s="15"/>
-      <c r="Q20" s="1">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -4209,11 +4249,8 @@
       <c r="J21" s="17"/>
       <c r="K21" s="3"/>
       <c r="L21" s="15"/>
-      <c r="Q21" s="1">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -4233,17 +4270,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="15"/>
+        <v>125</v>
+      </c>
+      <c r="H22" s="15">
+        <v>6</v>
+      </c>
       <c r="J22" s="17"/>
       <c r="K22" s="3"/>
       <c r="L22" s="15"/>
-      <c r="Q22" s="1">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -4263,7 +4299,7 @@
         <v>24</v>
       </c>
       <c r="G23" s="42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H23" s="41" t="s">
         <v>32</v>
@@ -4271,12 +4307,8 @@
       <c r="J23" s="17"/>
       <c r="K23" s="3"/>
       <c r="L23" s="15"/>
-      <c r="Q23" s="1">
-        <f>SUM(Q19:Q22)</f>
-        <v>6680</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -4293,10 +4325,10 @@
         <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="H24" s="15">
         <v>4</v>
@@ -4305,7 +4337,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="15"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -4325,7 +4357,7 @@
         <v>24</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H25" s="15">
         <v>4</v>
@@ -4334,7 +4366,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="15"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -4354,7 +4386,7 @@
         <v>24</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H26" s="15">
         <v>4</v>
@@ -4363,14 +4395,14 @@
       <c r="K26" s="3"/>
       <c r="L26" s="15"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3">
         <v>1000</v>
@@ -4383,7 +4415,7 @@
         <v>24</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H27" s="15">
         <v>4</v>
@@ -4392,14 +4424,14 @@
       <c r="K27" s="3"/>
       <c r="L27" s="15"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="3">
         <v>1000</v>
@@ -4412,7 +4444,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H28" s="15">
         <v>5</v>
@@ -4421,14 +4453,14 @@
       <c r="K28" s="3"/>
       <c r="L28" s="15"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
@@ -4440,7 +4472,7 @@
         <v>24</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H29" s="15">
         <v>5</v>
@@ -4449,59 +4481,89 @@
       <c r="K29" s="3"/>
       <c r="L29" s="15"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="3"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="15"/>
+      <c r="C30" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="3">
+        <v>90</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="15">
+        <v>6</v>
+      </c>
       <c r="J30" s="17"/>
       <c r="K30" s="3"/>
       <c r="L30" s="15"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="15"/>
+      <c r="C31" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="3">
+        <v>90</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H31" s="15">
+        <v>6</v>
+      </c>
       <c r="J31" s="17"/>
       <c r="K31" s="3"/>
       <c r="L31" s="15"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="15"/>
+      <c r="C32" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="3">
+        <v>310</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32" s="15">
+        <v>6</v>
+      </c>
       <c r="J32" s="17"/>
       <c r="K32" s="3"/>
       <c r="L32" s="15"/>
@@ -4512,14 +4574,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+      <c r="C33" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="3">
+        <v>310</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="H33" s="15"/>
       <c r="J33" s="17"/>
       <c r="K33" s="3"/>
@@ -4531,14 +4601,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+      <c r="C34" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="3">
+        <v>310</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="H34" s="15"/>
       <c r="J34" s="18"/>
       <c r="K34" s="19"/>
@@ -4550,14 +4628,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="C35" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="3">
+        <v>90</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="H35" s="15"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -4566,14 +4652,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+      <c r="C36" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="3">
+        <v>90</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -4582,14 +4676,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+      <c r="C37" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="3">
+        <v>90</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -4598,14 +4700,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="3"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="C38" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="3">
+        <v>90</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="H38" s="15"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -4614,14 +4724,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="C39" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="3">
+        <v>100</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="H39" s="15"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0471BF6-E09F-4A06-AADD-F3BC8B2EEF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300A91CC-4818-41A4-B961-B44A19F6A9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -449,7 +449,7 @@
     <t>JEPS-2026-000480534</t>
   </si>
   <si>
-    <t>Utanhg</t>
+    <t>MTC202610197121661</t>
   </si>
 </sst>
 </file>
@@ -758,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -881,6 +881,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1277,11 +1280,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="43">
+      <c r="J1" s="44">
         <v>6684</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="46"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -1327,7 +1330,7 @@
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
         <v>3815</v>
       </c>
-      <c r="P2" s="46">
+      <c r="P2" s="47">
         <f>SUM(O2:O4)</f>
         <v>4865</v>
       </c>
@@ -1374,7 +1377,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>570</v>
       </c>
-      <c r="P3" s="46"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
@@ -1419,7 +1422,7 @@
         <f>SUMIFS(E:E, H:H, "")</f>
         <v>480</v>
       </c>
-      <c r="P4" s="46"/>
+      <c r="P4" s="47"/>
       <c r="R4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3514,7 +3517,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U201"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3535,7 +3538,7 @@
     <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -3560,16 +3563,16 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="43">
+      <c r="J1" s="44">
         <v>6684</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="46"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -3607,14 +3610,14 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>1080</v>
-      </c>
-      <c r="P2" s="46">
+        <v>0</v>
+      </c>
+      <c r="P2" s="47">
         <f>SUM(O2:O4)</f>
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f t="shared" ref="A3:A55" si="0">A2+1</f>
         <v>2</v>
@@ -3655,9 +3658,9 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="46"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="P3" s="47"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3697,14 +3700,11 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>210</v>
-      </c>
-      <c r="P4" s="46"/>
-      <c r="T4" s="1">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="P4" s="47"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3740,15 +3740,8 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="9"/>
-      <c r="T5" s="1">
-        <f>P2-T4</f>
-        <v>355</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3784,7 +3777,7 @@
       </c>
       <c r="O6" s="25"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3825,7 +3818,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3863,10 +3856,10 @@
         <v>92</v>
       </c>
       <c r="O8" s="1">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3899,10 +3892,10 @@
       </c>
       <c r="O9" s="1">
         <f>O8-O7</f>
-        <v>870</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3931,7 +3924,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="15"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3960,7 +3953,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="15"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3989,7 +3982,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="15"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4018,7 +4011,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -4047,7 +4040,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -4076,7 +4069,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="15"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -4590,7 +4583,9 @@
       <c r="G33" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H33" s="15"/>
+      <c r="H33" s="15">
+        <v>7</v>
+      </c>
       <c r="J33" s="17"/>
       <c r="K33" s="3"/>
       <c r="L33" s="15"/>
@@ -4614,10 +4609,12 @@
       <c r="F34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="H34" s="15"/>
+      <c r="H34" s="15">
+        <v>7</v>
+      </c>
       <c r="J34" s="18"/>
       <c r="K34" s="19"/>
       <c r="L34" s="20"/>
@@ -4644,7 +4641,9 @@
       <c r="G35" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H35" s="15"/>
+      <c r="H35" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
@@ -4668,7 +4667,9 @@
       <c r="G36" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H36" s="15"/>
+      <c r="H36" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
@@ -4692,7 +4693,9 @@
       <c r="G37" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H37" s="15"/>
+      <c r="H37" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
@@ -4716,7 +4719,9 @@
       <c r="G38" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H38" s="15"/>
+      <c r="H38" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
@@ -4740,7 +4745,9 @@
       <c r="G39" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H39" s="15"/>
+      <c r="H39" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="17">
@@ -4755,7 +4762,9 @@
         <v/>
       </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300A91CC-4818-41A4-B961-B44A19F6A9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF3D4EE-4243-433B-8D8E-F9C8C6831EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="138">
   <si>
     <t>No.</t>
   </si>
@@ -428,9 +428,6 @@
     <t>JEPS-2026-000413773</t>
   </si>
   <si>
-    <t>Nelbelyn Omosura</t>
-  </si>
-  <si>
     <t>JEPS-2026-000447618</t>
   </si>
   <si>
@@ -450,6 +447,15 @@
   </si>
   <si>
     <t>MTC202610197121661</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000520250</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000520496</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000521242</t>
   </si>
 </sst>
 </file>
@@ -882,9 +888,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -896,6 +899,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1280,11 +1286,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="44">
+      <c r="J1" s="43">
         <v>6684</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="46"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -1330,7 +1336,7 @@
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
         <v>3815</v>
       </c>
-      <c r="P2" s="47">
+      <c r="P2" s="46">
         <f>SUM(O2:O4)</f>
         <v>4865</v>
       </c>
@@ -1377,7 +1383,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>570</v>
       </c>
-      <c r="P3" s="47"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
@@ -1422,7 +1428,7 @@
         <f>SUMIFS(E:E, H:H, "")</f>
         <v>480</v>
       </c>
-      <c r="P4" s="47"/>
+      <c r="P4" s="46"/>
       <c r="R4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3563,11 +3569,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="44">
+      <c r="J1" s="43">
         <v>6684</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="46"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -3610,11 +3616,11 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>0</v>
-      </c>
-      <c r="P2" s="47">
+        <v>400</v>
+      </c>
+      <c r="P2" s="46">
         <f>SUM(O2:O4)</f>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3658,7 +3664,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="47"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
@@ -3700,9 +3706,9 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="47"/>
+        <v>60</v>
+      </c>
+      <c r="P4" s="46"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
@@ -4581,7 +4587,7 @@
         <v>24</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H33" s="15">
         <v>7</v>
@@ -4609,8 +4615,8 @@
       <c r="F34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="43" t="s">
-        <v>128</v>
+      <c r="G34" s="47" t="s">
+        <v>137</v>
       </c>
       <c r="H34" s="15">
         <v>7</v>
@@ -4639,7 +4645,7 @@
         <v>24</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H35" s="15">
         <v>7</v>
@@ -4665,7 +4671,7 @@
         <v>24</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H36" s="15">
         <v>7</v>
@@ -4691,7 +4697,7 @@
         <v>24</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H37" s="15">
         <v>7</v>
@@ -4717,7 +4723,7 @@
         <v>24</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H38" s="15">
         <v>7</v>
@@ -4743,7 +4749,7 @@
         <v>24</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H39" s="15">
         <v>7</v>
@@ -4755,7 +4761,9 @@
         <v>39</v>
       </c>
       <c r="B40" s="3"/>
-      <c r="C40" s="34"/>
+      <c r="C40" s="34" t="s">
+        <v>85</v>
+      </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3" t="str">
         <f t="shared" si="1"/>
@@ -4763,7 +4771,7 @@
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H40" s="15"/>
     </row>
@@ -4773,14 +4781,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="C41" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="3">
+        <v>310</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -4789,14 +4805,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="3"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="C42" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="3">
+        <v>90</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="H42" s="15"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF3D4EE-4243-433B-8D8E-F9C8C6831EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC43539-6404-4310-8B63-EC0C0DA7EEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="141">
   <si>
     <t>No.</t>
   </si>
@@ -446,9 +446,6 @@
     <t>JEPS-2026-000480534</t>
   </si>
   <si>
-    <t>MTC202610197121661</t>
-  </si>
-  <si>
     <t>JEPS-2026-000520250</t>
   </si>
   <si>
@@ -456,6 +453,18 @@
   </si>
   <si>
     <t>JEPS-2026-000521242</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000539524</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000530343</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000541006</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000543020</t>
   </si>
 </sst>
 </file>
@@ -888,6 +897,9 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -899,9 +911,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1286,11 +1295,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="43">
+      <c r="J1" s="44">
         <v>6684</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="46"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -1336,7 +1345,7 @@
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
         <v>3815</v>
       </c>
-      <c r="P2" s="46">
+      <c r="P2" s="47">
         <f>SUM(O2:O4)</f>
         <v>4865</v>
       </c>
@@ -1383,7 +1392,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>570</v>
       </c>
-      <c r="P3" s="46"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
@@ -1428,7 +1437,7 @@
         <f>SUMIFS(E:E, H:H, "")</f>
         <v>480</v>
       </c>
-      <c r="P4" s="46"/>
+      <c r="P4" s="47"/>
       <c r="R4" s="1" t="s">
         <v>63</v>
       </c>
@@ -3569,11 +3578,11 @@
       <c r="H1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="43">
+      <c r="J1" s="44">
         <v>6684</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="46"/>
       <c r="M1" s="8"/>
       <c r="N1" s="6"/>
       <c r="O1" s="7"/>
@@ -3616,11 +3625,11 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>400</v>
-      </c>
-      <c r="P2" s="46">
+        <v>890</v>
+      </c>
+      <c r="P2" s="47">
         <f>SUM(O2:O4)</f>
-        <v>460</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3664,7 +3673,7 @@
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="46"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
@@ -3706,9 +3715,9 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>60</v>
-      </c>
-      <c r="P4" s="46"/>
+        <v>180</v>
+      </c>
+      <c r="P4" s="47"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
@@ -4615,8 +4624,8 @@
       <c r="F34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G34" s="47" t="s">
-        <v>137</v>
+      <c r="G34" s="43" t="s">
+        <v>136</v>
       </c>
       <c r="H34" s="15">
         <v>7</v>
@@ -4764,14 +4773,18 @@
       <c r="C40" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F40" s="3"/>
+      <c r="D40" s="3">
+        <v>310</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G40" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H40" s="15"/>
     </row>
@@ -4795,7 +4808,7 @@
         <v>24</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H41" s="15"/>
     </row>
@@ -4819,7 +4832,7 @@
         <v>24</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H42" s="15"/>
     </row>
@@ -4829,14 +4842,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
+      <c r="C43" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="3">
+        <v>90</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="H43" s="15"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -4845,14 +4866,21 @@
         <v>43</v>
       </c>
       <c r="B44" s="3"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="C44" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>30</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="H44" s="15"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -4861,14 +4889,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="3"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="C45" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="D45" s="3">
+        <v>90</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H45" s="15"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC43539-6404-4310-8B63-EC0C0DA7EEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEE5EC-D31B-41D9-A551-02495AD7AF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
     <sheet name="All" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3625,11 +3625,11 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="P2" s="47">
         <f>SUM(O2:O4)</f>
-        <v>1070</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="P4" s="47"/>
     </row>
@@ -3871,7 +3871,7 @@
         <v>92</v>
       </c>
       <c r="O8" s="1">
-        <v>2550</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="O9" s="1">
         <f>O8-O7</f>
-        <v>990</v>
+        <v>950</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4786,7 +4786,9 @@
       <c r="G40" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H40" s="15"/>
+      <c r="H40" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="17">
@@ -4810,7 +4812,9 @@
       <c r="G41" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H41" s="15"/>
+      <c r="H41" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="17">
@@ -4834,7 +4838,9 @@
       <c r="G42" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="15"/>
+      <c r="H42" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="17">
@@ -4858,7 +4864,9 @@
       <c r="G43" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H43" s="15"/>
+      <c r="H43" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="17">
@@ -4881,7 +4889,9 @@
       <c r="G44" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H44" s="15"/>
+      <c r="H44" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="17">
@@ -4905,7 +4915,9 @@
       <c r="G45" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H45" s="15"/>
+      <c r="H45" s="15">
+        <v>8</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="17">
